--- a/data/raw/inventory/Week 31/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F10" t="n">
         <v>116</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
         <v>36</v>
@@ -1961,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 31/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -585,7 +585,7 @@
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>13</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>11</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1713,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
